--- a/templates/planilla_examenes_preocupacionales.xlsx
+++ b/templates/planilla_examenes_preocupacionales.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\diseño-afk\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B9CA4F-2751-4370-95F4-D554ACFD4046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{408EC103-A9B8-46DE-820C-967A90211FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="0" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja 1" sheetId="3" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="3" r:id="rId1"/>
     <sheet name="rangos dr" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -717,7 +717,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -770,11 +770,6 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -811,7 +806,11 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1039,186 +1038,186 @@
   <dimension ref="A1:CD1"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:82" s="33" customFormat="1" ht="36.75" customHeight="1" thickBot="1">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:82" ht="36.75" customHeight="1" thickBot="1">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="26"/>
-      <c r="H1" s="27" t="s">
+      <c r="G1" s="23"/>
+      <c r="H1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="27" t="s">
+      <c r="J1" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="27" t="s">
+      <c r="L1" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="27" t="s">
+      <c r="M1" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="27" t="s">
+      <c r="N1" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="28" t="s">
+      <c r="O1" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="28" t="s">
+      <c r="P1" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="28" t="s">
+      <c r="Q1" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="27" t="s">
+      <c r="R1" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="28" t="s">
+      <c r="S1" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="28" t="s">
+      <c r="T1" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="27" t="s">
+      <c r="U1" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="28" t="s">
+      <c r="V1" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="27" t="s">
+      <c r="W1" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="27" t="s">
+      <c r="X1" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="27" t="s">
+      <c r="Y1" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="28" t="s">
+      <c r="Z1" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="28" t="s">
+      <c r="AA1" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="27" t="s">
+      <c r="AB1" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="27" t="s">
+      <c r="AC1" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="27" t="s">
+      <c r="AD1" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="27" t="s">
+      <c r="AE1" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="28" t="s">
+      <c r="AF1" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="27" t="s">
+      <c r="AG1" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="27" t="s">
+      <c r="AH1" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="27" t="s">
+      <c r="AI1" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="28" t="s">
+      <c r="AJ1" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="28" t="s">
+      <c r="AK1" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="AL1" s="28" t="s">
+      <c r="AL1" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="AM1" s="28" t="s">
+      <c r="AM1" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="AN1" s="28" t="s">
+      <c r="AN1" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="28" t="s">
+      <c r="AO1" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="AP1" s="28" t="s">
+      <c r="AP1" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="AQ1" s="28" t="s">
+      <c r="AQ1" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="AR1" s="28" t="s">
+      <c r="AR1" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="AS1" s="29" t="s">
+      <c r="AS1" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="AT1" s="29" t="s">
+      <c r="AT1" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="AU1" s="29" t="s">
+      <c r="AU1" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="AV1" s="29" t="s">
+      <c r="AV1" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="AW1" s="29" t="s">
+      <c r="AW1" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="AX1" s="29" t="s">
+      <c r="AX1" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="AY1" s="29" t="s">
+      <c r="AY1" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="AZ1" s="29" t="s">
+      <c r="AZ1" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="BA1" s="29" t="s">
+      <c r="BA1" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="BB1" s="29" t="s">
+      <c r="BB1" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="BC1" s="29" t="s">
+      <c r="BC1" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="BD1" s="30" t="s">
+      <c r="BD1" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="BE1" s="31" t="s">
+      <c r="BE1" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="BF1" s="31" t="s">
+      <c r="BF1" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="BG1" s="31" t="s">
+      <c r="BG1" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="BH1" s="31" t="s">
+      <c r="BH1" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="BI1" s="32" t="s">
+      <c r="BI1" s="29" t="s">
         <v>59</v>
       </c>
       <c r="BJ1" s="1"/>
@@ -1414,7 +1413,7 @@
       <c r="D13" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="30" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1428,7 +1427,7 @@
       <c r="D14" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="E14" s="19"/>
+      <c r="E14" s="31"/>
     </row>
     <row r="15" spans="2:5" ht="14.5">
       <c r="B15" s="12" t="s">
@@ -1530,7 +1529,7 @@
       <c r="D22" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="30" t="s">
         <v>108</v>
       </c>
     </row>
@@ -1544,7 +1543,7 @@
       <c r="D23" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="E23" s="20"/>
+      <c r="E23" s="32"/>
     </row>
     <row r="24" spans="2:5" ht="15.75" customHeight="1">
       <c r="B24" s="12" t="s">
@@ -1556,7 +1555,7 @@
       <c r="D24" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="E24" s="19"/>
+      <c r="E24" s="31"/>
     </row>
     <row r="25" spans="2:5" ht="15.75" customHeight="1">
       <c r="B25" s="12"/>
